--- a/paper_trades/dashboard_2026-06-11.xlsx
+++ b/paper_trades/dashboard_2026-06-11.xlsx
@@ -5812,7 +5812,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>محسوب في: 2026-06-11T02:02:31</t>
+          <t>محسوب في: 2026-06-11T06:33:01</t>
         </is>
       </c>
     </row>

--- a/paper_trades/dashboard_2026-06-11.xlsx
+++ b/paper_trades/dashboard_2026-06-11.xlsx
@@ -5812,7 +5812,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>محسوب في: 2026-06-11T06:33:01</t>
+          <t>محسوب في: 2026-06-11T07:07:08</t>
         </is>
       </c>
     </row>
